--- a/stories/arbres/TREE-TMP-005.xlsx
+++ b/stories/arbres/TREE-TMP-005.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léa est au bord de la mer, avec maman. Le sable est tiède. Maman dit : il y a quatre saisons. Un signe chacune. Printemps, les fleurs. Été, c'est chaud. Automne, les feuilles. Hiver, le manteau. Léa écoute. Quatre saisons. Un signe chacune. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
+          <t>Léa est au bord de la mer, avec maman. Le sable est tiède. Il y a quatre saisons. Un signe chacune. Printemps, les fleurs. Été, c'est chaud. Automne, les feuilles. Hiver, le manteau. Léa écoute. Quatre saisons. Un signe chacune. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Léa est au bord de la mer, avec maman. Le sable est tiède.
+maman|Il y a quatre saisons.
+narrateur|Un signe chacune. Printemps, les fleurs. Été, c'est chaud. Automne, les feuilles. Hiver, le manteau. Léa écoute. Quatre saisons. Un signe chacune. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1515,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1544,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Léa pose une pomme. Maman dit : automne, les pommes, les feuilles. Quatre saisons. Un signe chacune. Printemps fleurs. Été chaud. Hiver manteau. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
+          <t>Léa pose une pomme. Automne, les pommes, les feuilles. Quatre saisons. Un signe chacune. Printemps fleurs. Été chaud. Hiver manteau. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1682,13 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Léa pose une pomme.
+maman|Automne, les pommes, les feuilles. Quatre saisons.
+narrateur|Un signe chacune. Printemps fleurs. Été chaud. Hiver manteau. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1865,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Combien de saisons ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2038,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a dit les quatre saisons. Un signe chacune. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2229,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2396,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers la cuisine. Le sable est tiède. Dans la cuisine, une fleur dans un verre. Printemps. Quatre saisons. Un signe chacune. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2587,11 @@
         <v>12</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2754,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde les cubes tout près. La lumière est claire. On range la chaise. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. La mer chante. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2921,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3088,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le livre tout près. Des miettes dorment sur la table. On range un objet. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le sable colle aux doigts. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Maman serre Léa tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3255,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3422,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde la dînette tout près. Un chat miaule une fois. On se tient la main. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. On a nommé un signe. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3589,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3756,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers le jardin. Une pomme sent le sucré. Dans le jardin, c'est un peu chaud. Été. Quatre saisons. Un signe chacune. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3947,11 @@
         <v>12</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3875,7 +3976,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Léa garde les cubes tout près. Les chaussures font toc toc. On dit merci. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le manteau attend l'hiver. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa range. Maman dit : c'est bien.</t>
+          <t>Léa garde les cubes tout près. Les chaussures font toc toc. On dit merci. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le manteau attend l'hiver. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa range. C'est bien.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4013,6 +4114,12 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde les cubes tout près. Les chaussures font toc toc. On dit merci. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le manteau attend l'hiver. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4282,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4449,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le livre tout près. La couverture est douce. On souffle doucement. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. La mer chante. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. On souffle. Léa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4616,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4783,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde la dînette tout près. Une cloche tinte au loin. On écoute jusqu'au bout. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le sable colle aux doigts. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4950,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5117,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers la chambre. Une cloche tinte au loin. Dans la chambre, le manteau est sur la chaise. Hiver. Quatre saisons. Un signe chacune. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5308,11 @@
         <v>12</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5475,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde les cubes tout près. Le bois sent le chaud. On attend son tour. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. On a nommé un signe. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5642,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5809,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le livre tout près. Une goutte tombe, ploc. On sourit ensemble. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le manteau attend l'hiver. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Maman serre Léa tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5976,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6143,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde la dînette tout près. Le savon sent la fleur. On pose les pieds par terre. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. La mer chante. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6310,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6305,6 +6477,11 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Léa pose un yaourt, froid. Comme l'hiver. Hiver, manteau. Quatre saisons. Un signe chacune. Léa répète : hiver. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6481,6 +6658,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|L'hiver, on met quoi ?</t>
         </is>
       </c>
     </row>
@@ -6649,6 +6831,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Printemps fleurs. Été chaud. Automne feuilles. Hiver manteau. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6835,6 +7022,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6997,6 +7189,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers la cuisine. Le savon mousse entre les doigts. Ça sent le pain. Automne, une feuille à la fenêtre. Quatre saisons. Un signe chacune. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7183,6 +7380,11 @@
         <v>12</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7207,7 +7409,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Léa garde les cubes tout près. Le tissu est tout doux. On parle tout bas. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le sable colle aux doigts. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa range. Maman dit : c'est bien.</t>
+          <t>Léa garde les cubes tout près. Le tissu est tout doux. On parle tout bas. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le sable colle aux doigts. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa range. C'est bien.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7345,6 +7547,12 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde les cubes tout près. Le tissu est tout doux. On parle tout bas. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le sable colle aux doigts. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7507,6 +7715,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7669,6 +7882,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le livre tout près. Une cuillère tinte. On range les jouets. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. On a nommé un signe. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. On souffle. Léa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7831,6 +8049,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7993,6 +8216,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde la dînette tout près. Le sable est tiède. On s'assoit un moment. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le manteau attend l'hiver. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8155,6 +8383,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8317,6 +8550,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers le jardin. Ça sent le pain tiède. L'herbe est verte. Printemps fleurs. Quatre saisons. Un signe chacune. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8503,6 +8741,11 @@
         <v>12</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8665,6 +8908,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde les cubes tout près. Un rire court, tout petit. On respire, un, deux. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. La mer chante. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8827,6 +9075,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8989,6 +9242,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le livre tout près. Le papier froisse, chut. On referme le sac. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le sable colle aux doigts. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Maman serre Léa tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9151,6 +9409,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9313,6 +9576,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde la dînette tout près. L'herbe chatouille le mollet. On essuie une miette. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. On a nommé un signe. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9475,6 +9743,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9637,6 +9910,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers la chambre. La terre est un peu humide. Le doudou est chaud. Hiver manteau. Quatre saisons. Un signe chacune. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9823,6 +10101,11 @@
         <v>12</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9847,7 +10130,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Léa garde les cubes tout près. Un pigeon roucoule. On met le doudou près. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le manteau attend l'hiver. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa range. Maman dit : c'est bien.</t>
+          <t>Léa garde les cubes tout près. Un pigeon roucoule. On met le doudou près. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le manteau attend l'hiver. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa range. C'est bien.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -9985,6 +10268,12 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde les cubes tout près. Un pigeon roucoule. On met le doudou près. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le manteau attend l'hiver. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10147,6 +10436,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10309,6 +10603,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le livre tout près. La fenêtre vibre un peu. On lace les chaussures. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. La mer chante. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. On souffle. Léa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10471,6 +10770,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10633,6 +10937,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde la dînette tout près. Le lait est froid dans le verre. On met le manteau. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le sable colle aux doigts. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10795,6 +11104,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10957,6 +11271,11 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Léa pose un morceau de pain. Maman parle de l'été, chaud. Quatre saisons. Un signe chacune. Printemps fleurs. Automne feuilles. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11133,6 +11452,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Le printemps, on voit quoi ?</t>
         </is>
       </c>
     </row>
@@ -11301,6 +11625,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Quatre saisons. Léa a nommé un signe. Maman sourit. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11487,6 +11816,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11649,6 +11983,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers la cuisine. Le banc est lisse. Léa lave une tasse. Maman dit été chaud. Quatre saisons. Un signe chacune. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11835,6 +12174,11 @@
         <v>12</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11997,6 +12341,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde les cubes tout près. La corde du sac est rêche. On boit une gorgée. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. On a nommé un signe. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12159,6 +12508,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12321,6 +12675,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le livre tout près. Le savon mousse entre les doigts. On feuillette le livre. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le manteau attend l'hiver. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Maman serre Léa tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12483,6 +12842,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12645,6 +13009,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde la dînette tout près. Un ruisseau chante. On referme le livre. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. La mer chante. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12807,6 +13176,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12969,6 +13343,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers le jardin. Un ballon frotte le sol. Une feuille tombe. Automne. Quatre saisons. Un signe chacune. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13155,6 +13534,11 @@
         <v>12</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13179,7 +13563,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Léa garde les cubes tout près. La laine gratte un peu. On pose le ballon. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le sable colle aux doigts. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa range. Maman dit : c'est bien.</t>
+          <t>Léa garde les cubes tout près. La laine gratte un peu. On pose le ballon. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le sable colle aux doigts. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa range. C'est bien.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13317,6 +13701,12 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde les cubes tout près. La laine gratte un peu. On pose le ballon. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le sable colle aux doigts. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13479,6 +13869,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13641,6 +14036,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le livre tout près. Un pain croustille. On secoue le sable. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. On a nommé un signe. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. On souffle. Léa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13803,6 +14203,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13965,6 +14370,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde la dînette tout près. Le savon glisse. On caresse le tissu. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le manteau attend l'hiver. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14127,6 +14537,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14289,6 +14704,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers la chambre. Le papier froisse, chut. Léa touche le manteau. Hiver. Quatre saisons. Un signe chacune. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14475,6 +14895,11 @@
         <v>12</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14637,6 +15062,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde les cubes tout près. Une plume vole. On tend la main. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. La mer chante. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14799,6 +15229,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14961,6 +15396,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le livre tout près. Le banc est lisse. On chante un petit air. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le sable colle aux doigts. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Maman serre Léa tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15123,6 +15563,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15285,6 +15730,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde la dînette tout près. Un grelot sonne. On compte jusqu'à trois. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. On a nommé un signe. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15447,6 +15897,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15465,7 +15920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15482,6 +15937,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-TMP-005.xlsx
+++ b/stories/arbres/TREE-TMP-005.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Un signe chacune. Printemps, les fleurs. Été, c'est chaud. Automne, les feuilles. Hiver, le manteau. Léa écoute. Quatre saisons. Un signe chacune. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1520,6 +1526,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1689,6 +1696,7 @@
 narrateur|Un signe chacune. Printemps fleurs. Été chaud. Hiver manteau. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1872,6 +1880,7 @@
           <t>narrateur|Combien de saisons ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2043,6 +2052,7 @@
           <t>narrateur|Léa a dit les quatre saisons. Un signe chacune. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2234,6 +2244,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2401,6 +2412,7 @@
           <t>narrateur|Léa va vers la cuisine. Le sable est tiède. Dans la cuisine, une fleur dans un verre. Printemps. Quatre saisons. Un signe chacune. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2592,6 +2604,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2759,6 +2772,7 @@
           <t>narrateur|Léa garde les cubes tout près. La lumière est claire. On range la chaise. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. La mer chante. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2926,6 +2940,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3093,6 +3108,7 @@
           <t>narrateur|Léa garde le livre tout près. Des miettes dorment sur la table. On range un objet. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le sable colle aux doigts. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Maman serre Léa tout doux.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3260,6 +3276,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3427,6 +3444,7 @@
           <t>narrateur|Léa garde la dînette tout près. Un chat miaule une fois. On se tient la main. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. On a nommé un signe. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3594,6 +3612,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3761,6 +3780,7 @@
           <t>narrateur|Léa va vers le jardin. Une pomme sent le sucré. Dans le jardin, c'est un peu chaud. Été. Quatre saisons. Un signe chacune. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3952,6 +3972,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4120,6 +4141,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4287,6 +4309,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4454,6 +4477,7 @@
           <t>narrateur|Léa garde le livre tout près. La couverture est douce. On souffle doucement. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. La mer chante. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. On souffle. Léa sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4621,6 +4645,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4788,6 +4813,7 @@
           <t>narrateur|Léa garde la dînette tout près. Une cloche tinte au loin. On écoute jusqu'au bout. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le sable colle aux doigts. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4955,6 +4981,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5122,6 +5149,7 @@
           <t>narrateur|Léa va vers la chambre. Une cloche tinte au loin. Dans la chambre, le manteau est sur la chaise. Hiver. Quatre saisons. Un signe chacune. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5313,6 +5341,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5480,6 +5509,7 @@
           <t>narrateur|Léa garde les cubes tout près. Le bois sent le chaud. On attend son tour. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. On a nommé un signe. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5647,6 +5677,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5814,6 +5845,7 @@
           <t>narrateur|Léa garde le livre tout près. Une goutte tombe, ploc. On sourit ensemble. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le manteau attend l'hiver. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Maman serre Léa tout doux.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5981,6 +6013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6148,6 +6181,7 @@
           <t>narrateur|Léa garde la dînette tout près. Le savon sent la fleur. On pose les pieds par terre. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. La mer chante. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6315,6 +6349,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6482,6 +6517,7 @@
           <t>narrateur|Léa pose un yaourt, froid. Comme l'hiver. Hiver, manteau. Quatre saisons. Un signe chacune. Léa répète : hiver. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6665,6 +6701,7 @@
           <t>narrateur|L'hiver, on met quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6836,6 +6873,7 @@
           <t>narrateur|Printemps fleurs. Été chaud. Automne feuilles. Hiver manteau. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7027,6 +7065,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7194,6 +7233,7 @@
           <t>narrateur|Léa va vers la cuisine. Le savon mousse entre les doigts. Ça sent le pain. Automne, une feuille à la fenêtre. Quatre saisons. Un signe chacune. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7385,6 +7425,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7553,6 +7594,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7720,6 +7762,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7887,6 +7930,7 @@
           <t>narrateur|Léa garde le livre tout près. Une cuillère tinte. On range les jouets. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. On a nommé un signe. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. On souffle. Léa sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8054,6 +8098,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8221,6 +8266,7 @@
           <t>narrateur|Léa garde la dînette tout près. Le sable est tiède. On s'assoit un moment. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le manteau attend l'hiver. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8388,6 +8434,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8555,6 +8602,7 @@
           <t>narrateur|Léa va vers le jardin. Ça sent le pain tiède. L'herbe est verte. Printemps fleurs. Quatre saisons. Un signe chacune. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8746,6 +8794,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8913,6 +8962,7 @@
           <t>narrateur|Léa garde les cubes tout près. Un rire court, tout petit. On respire, un, deux. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. La mer chante. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9080,6 +9130,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9247,6 +9298,7 @@
           <t>narrateur|Léa garde le livre tout près. Le papier froisse, chut. On referme le sac. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le sable colle aux doigts. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Maman serre Léa tout doux.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9414,6 +9466,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9581,6 +9634,7 @@
           <t>narrateur|Léa garde la dînette tout près. L'herbe chatouille le mollet. On essuie une miette. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. On a nommé un signe. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9748,6 +9802,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9915,6 +9970,7 @@
           <t>narrateur|Léa va vers la chambre. La terre est un peu humide. Le doudou est chaud. Hiver manteau. Quatre saisons. Un signe chacune. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10106,6 +10162,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10274,6 +10331,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10441,6 +10499,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10608,6 +10667,7 @@
           <t>narrateur|Léa garde le livre tout près. La fenêtre vibre un peu. On lace les chaussures. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. La mer chante. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. On souffle. Léa sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10775,6 +10835,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10942,6 +11003,7 @@
           <t>narrateur|Léa garde la dînette tout près. Le lait est froid dans le verre. On met le manteau. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le sable colle aux doigts. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11109,6 +11171,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11276,6 +11339,7 @@
           <t>narrateur|Léa pose un morceau de pain. Maman parle de l'été, chaud. Quatre saisons. Un signe chacune. Printemps fleurs. Automne feuilles. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11459,6 +11523,7 @@
           <t>narrateur|Le printemps, on voit quoi ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11630,6 +11695,7 @@
           <t>narrateur|Quatre saisons. Léa a nommé un signe. Maman sourit. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11821,6 +11887,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11988,6 +12055,7 @@
           <t>narrateur|Léa va vers la cuisine. Le banc est lisse. Léa lave une tasse. Maman dit été chaud. Quatre saisons. Un signe chacune. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12179,6 +12247,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12346,6 +12415,7 @@
           <t>narrateur|Léa garde les cubes tout près. La corde du sac est rêche. On boit une gorgée. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. On a nommé un signe. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12513,6 +12583,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12680,6 +12751,7 @@
           <t>narrateur|Léa garde le livre tout près. Le savon mousse entre les doigts. On feuillette le livre. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le manteau attend l'hiver. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Maman serre Léa tout doux.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12847,6 +12919,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13014,6 +13087,7 @@
           <t>narrateur|Léa garde la dînette tout près. Un ruisseau chante. On referme le livre. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. La mer chante. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13181,6 +13255,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13348,6 +13423,7 @@
           <t>narrateur|Léa va vers le jardin. Un ballon frotte le sol. Une feuille tombe. Automne. Quatre saisons. Un signe chacune. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13539,6 +13615,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13707,6 +13784,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13874,6 +13952,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14041,6 +14120,7 @@
           <t>narrateur|Léa garde le livre tout près. Un pain croustille. On secoue le sable. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. On a nommé un signe. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. On souffle. Léa sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14208,6 +14288,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14375,6 +14456,7 @@
           <t>narrateur|Léa garde la dînette tout près. Le savon glisse. On caresse le tissu. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le manteau attend l'hiver. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14542,6 +14624,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14709,6 +14792,7 @@
           <t>narrateur|Léa va vers la chambre. Le papier froisse, chut. Léa touche le manteau. Hiver. Quatre saisons. Un signe chacune. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14900,6 +14984,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15067,6 +15152,7 @@
           <t>narrateur|Léa garde les cubes tout près. Une plume vole. On tend la main. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. La mer chante. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15234,6 +15320,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15401,6 +15488,7 @@
           <t>narrateur|Léa garde le livre tout près. Le banc est lisse. On chante un petit air. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Le sable colle aux doigts. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Maman serre Léa tout doux.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15568,6 +15656,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15735,6 +15824,7 @@
           <t>narrateur|Léa garde la dînette tout près. Un grelot sonne. On compte jusqu'à trois. Quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. On a nommé un signe. Il y a quatre saisons. Un signe chacune. Printemps fleurs, été chaud, automne feuilles, hiver manteau. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15902,6 +15992,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15920,7 +16011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15944,6 +16035,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15958,7 +16063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16145,6 +16250,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
